--- a/artfynd/A 16286-2026 artfynd.xlsx
+++ b/artfynd/A 16286-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1826,6 +1826,999 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133018934</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>489773</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6608473</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133019472</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>489832</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6608510</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133019534</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>489831</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6608511</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133017186</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>489579</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6608344</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133023423</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>489836</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6608471</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133017684</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>489735</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6608332</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133016054</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57951</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>489591</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6608282</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133019654</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>489829</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6608544</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133017602</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>489715</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6608321</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16286-2026 artfynd.xlsx
+++ b/artfynd/A 16286-2026 artfynd.xlsx
@@ -2378,7 +2378,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133023423</v>
+        <v>133017684</v>
       </c>
       <c r="B17" t="n">
         <v>57145</v>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489836</v>
+        <v>489735</v>
       </c>
       <c r="R17" t="n">
-        <v>6608471</v>
+        <v>6608332</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,7 +2490,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133017684</v>
+        <v>133023423</v>
       </c>
       <c r="B18" t="n">
         <v>57145</v>
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489735</v>
+        <v>489836</v>
       </c>
       <c r="R18" t="n">
-        <v>6608332</v>
+        <v>6608471</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 16286-2026 artfynd.xlsx
+++ b/artfynd/A 16286-2026 artfynd.xlsx
@@ -2266,38 +2266,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133016054</v>
+        <v>133023423</v>
       </c>
       <c r="B16" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489591</v>
+        <v>489836</v>
       </c>
       <c r="R16" t="n">
-        <v>6608282</v>
+        <v>6608471</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,38 +2490,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133023423</v>
+        <v>133016054</v>
       </c>
       <c r="B18" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489836</v>
+        <v>489591</v>
       </c>
       <c r="R18" t="n">
-        <v>6608471</v>
+        <v>6608282</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 16286-2026 artfynd.xlsx
+++ b/artfynd/A 16286-2026 artfynd.xlsx
@@ -2266,7 +2266,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133023423</v>
+        <v>133017684</v>
       </c>
       <c r="B16" t="n">
         <v>57145</v>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489836</v>
+        <v>489735</v>
       </c>
       <c r="R16" t="n">
-        <v>6608471</v>
+        <v>6608332</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,38 +2378,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133017684</v>
+        <v>133016054</v>
       </c>
       <c r="B17" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489735</v>
+        <v>489591</v>
       </c>
       <c r="R17" t="n">
-        <v>6608332</v>
+        <v>6608282</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,38 +2490,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133016054</v>
+        <v>133023423</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489591</v>
+        <v>489836</v>
       </c>
       <c r="R18" t="n">
-        <v>6608282</v>
+        <v>6608471</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 16286-2026 artfynd.xlsx
+++ b/artfynd/A 16286-2026 artfynd.xlsx
@@ -2266,7 +2266,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133017684</v>
+        <v>133023423</v>
       </c>
       <c r="B16" t="n">
         <v>57145</v>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489735</v>
+        <v>489836</v>
       </c>
       <c r="R16" t="n">
-        <v>6608332</v>
+        <v>6608471</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,38 +2378,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133016054</v>
+        <v>133017684</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489591</v>
+        <v>489735</v>
       </c>
       <c r="R17" t="n">
-        <v>6608282</v>
+        <v>6608332</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,38 +2490,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133023423</v>
+        <v>133016054</v>
       </c>
       <c r="B18" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489836</v>
+        <v>489591</v>
       </c>
       <c r="R18" t="n">
-        <v>6608471</v>
+        <v>6608282</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 16286-2026 artfynd.xlsx
+++ b/artfynd/A 16286-2026 artfynd.xlsx
@@ -2266,38 +2266,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133023423</v>
+        <v>133016054</v>
       </c>
       <c r="B16" t="n">
-        <v>57145</v>
+        <v>57955</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489836</v>
+        <v>489591</v>
       </c>
       <c r="R16" t="n">
-        <v>6608471</v>
+        <v>6608282</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,7 +2378,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133017684</v>
+        <v>133023423</v>
       </c>
       <c r="B17" t="n">
         <v>57145</v>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489735</v>
+        <v>489836</v>
       </c>
       <c r="R17" t="n">
-        <v>6608332</v>
+        <v>6608471</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,38 +2490,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133016054</v>
+        <v>133017684</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>57145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489591</v>
+        <v>489735</v>
       </c>
       <c r="R18" t="n">
-        <v>6608282</v>
+        <v>6608332</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 16286-2026 artfynd.xlsx
+++ b/artfynd/A 16286-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1828,7 +1828,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133018934</v>
+        <v>133017186</v>
       </c>
       <c r="B12" t="n">
         <v>57145</v>
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489773</v>
+        <v>489579</v>
       </c>
       <c r="R12" t="n">
-        <v>6608473</v>
+        <v>6608344</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,27 +1940,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133019472</v>
+        <v>133016054</v>
       </c>
       <c r="B13" t="n">
-        <v>56908</v>
+        <v>57955</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208260</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1969,16 +1969,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489832</v>
+        <v>489591</v>
       </c>
       <c r="R13" t="n">
-        <v>6608510</v>
+        <v>6608282</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2010,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,780 +2049,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>133019534</v>
-      </c>
-      <c r="B14" t="n">
-        <v>57145</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>489831</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6608511</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>133017186</v>
-      </c>
-      <c r="B15" t="n">
-        <v>57145</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>489579</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6608344</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>133016054</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57955</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>489591</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6608282</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>133023423</v>
-      </c>
-      <c r="B17" t="n">
-        <v>57145</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>489836</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6608471</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>133017684</v>
-      </c>
-      <c r="B18" t="n">
-        <v>57145</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>489735</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6608332</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>133019654</v>
-      </c>
-      <c r="B19" t="n">
-        <v>57145</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>489829</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6608544</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>133017602</v>
-      </c>
-      <c r="B20" t="n">
-        <v>57145</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>489715</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6608321</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16286-2026 artfynd.xlsx
+++ b/artfynd/A 16286-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95683208</v>
+        <v>95999536</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Rågrecken, Vstm</t>
+          <t>Norr Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489627.5228208077</v>
+        <v>489598</v>
       </c>
       <c r="R2" t="n">
-        <v>6608284.975027382</v>
+        <v>6608321</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,51 +765,55 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95683292</v>
+        <v>95683334</v>
       </c>
       <c r="B3" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489625.1045633153</v>
+        <v>489638</v>
       </c>
       <c r="R3" t="n">
-        <v>6608326.982437552</v>
+        <v>6608375</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -856,19 +854,9 @@
           <t>2021-08-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,19 +883,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95683334</v>
+        <v>95683335</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -935,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489638.4168315291</v>
+        <v>489841</v>
       </c>
       <c r="R4" t="n">
-        <v>6608375.01814393</v>
+        <v>6608463</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -968,19 +951,9 @@
           <t>2021-08-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,16 +983,11 @@
         <v>95683336</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1047,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489831.4367591485</v>
+        <v>489832</v>
       </c>
       <c r="R5" t="n">
-        <v>6608522.245390104</v>
+        <v>6608522</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1080,19 +1048,9 @@
           <t>2021-08-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,53 +1077,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95683248</v>
+        <v>95999537</v>
       </c>
       <c r="B6" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N Rågrecken, Vstm</t>
+          <t>Norr Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489858.9256128868</v>
+        <v>489689</v>
       </c>
       <c r="R6" t="n">
-        <v>6608565.68694947</v>
+        <v>6608414</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,22 +1151,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,69 +1167,78 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95683247</v>
+        <v>95999539</v>
       </c>
       <c r="B7" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6428</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N Rågrecken, Vstm</t>
+          <t>Norr Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489627.0747375483</v>
+        <v>489684</v>
       </c>
       <c r="R7" t="n">
-        <v>6608306.229700867</v>
+        <v>6608391</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,22 +1262,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,66 +1278,75 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95999535</v>
+        <v>95999540</v>
       </c>
       <c r="B8" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norr Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489620.2621962824</v>
+        <v>489722</v>
       </c>
       <c r="R8" t="n">
-        <v>6608225.788501368</v>
+        <v>6608293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,19 +1376,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,15 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95999539</v>
+        <v>95683208</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,46 +1421,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norr Rågrecken, Vstm</t>
+          <t>N Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489684.0803027172</v>
+        <v>489627</v>
       </c>
       <c r="R9" t="n">
-        <v>6608390.578870736</v>
+        <v>6608285</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,22 +1475,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,58 +1491,48 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95999540</v>
+        <v>95999538</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1635,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489722.3375222438</v>
+        <v>489689</v>
       </c>
       <c r="R10" t="n">
-        <v>6608293.316422128</v>
+        <v>6608413</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,19 +1584,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,62 +1618,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95999536</v>
+        <v>95683247</v>
       </c>
       <c r="B11" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>6428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr Rågrecken, Vstm</t>
+          <t>N Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489598</v>
+        <v>489627</v>
       </c>
       <c r="R11" t="n">
-        <v>6608321</v>
+        <v>6608306</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1791,12 +1683,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,31 +1699,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133017186</v>
+        <v>95683248</v>
       </c>
       <c r="B12" t="n">
-        <v>57145</v>
+        <v>75300</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,42 +1726,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6428</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+          <t>N Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489579</v>
+        <v>489859</v>
       </c>
       <c r="R12" t="n">
-        <v>6608344</v>
+        <v>6608566</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1898,22 +1780,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,12 +1800,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1943,11 +1815,11 @@
         <v>133016054</v>
       </c>
       <c r="B13" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2049,6 +1921,689 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133825653</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>489716</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6608240</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska hack i död tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133014666</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>489583</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6608246</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133017186</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>489579</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6608344</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133825795</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>489730</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6608273</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>95999535</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norr Rågrecken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>489620</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6608226</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>95683292</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>N Rågrecken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>489625</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6608327</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16286-2026 artfynd.xlsx
+++ b/artfynd/A 16286-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999536</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683334</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683335</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683336</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999537</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999539</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999540</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683208</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999538</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683247</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683248</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1921,6 +1981,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133016054</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825653</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133014666</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2287,6 +2362,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133017186</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2409,6 +2489,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133825795</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2511,6 +2596,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999535</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2604,8 +2694,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683292</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>